--- a/data/trans_camb/P42C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Edad-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,22 +517,16 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -555,16 +547,6 @@
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2012</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2023/2012</t>
         </is>
@@ -577,8 +559,6 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -593,12 +573,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,01</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,16 +587,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,01</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,41</t>
         </is>
@@ -631,32 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,72; 1,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,62; 27,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 2,22</t>
+          <t>-13,72; 1,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 28,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,02; 2,22</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,53; 28,93</t>
+          <t>-1,62; 27,62</t>
         </is>
       </c>
     </row>
@@ -669,12 +629,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-22,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -683,16 +643,6 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,3%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>46,04%</t>
         </is>
@@ -707,32 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,21; 9,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,09; 115,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,1; 9,9</t>
+          <t>-43,21; 9,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 122,97</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-45,1; 9,9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,2; 122,97</t>
+          <t>-6,09; 115,19</t>
         </is>
       </c>
     </row>
@@ -749,12 +689,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,43</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,33</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -763,16 +703,6 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,43</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-7,33</t>
         </is>
@@ -787,32 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,99; -2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,32; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -2,87</t>
+          <t>-13,99; -2,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 2,97</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-13,7; -2,87</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-21,47; 2,97</t>
+          <t>-22,32; 3,24</t>
         </is>
       </c>
     </row>
@@ -825,12 +745,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-28,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-24,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -839,16 +759,6 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-24,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-28,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-24,65%</t>
         </is>
@@ -863,32 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,84; -10,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,76; 12,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,24; -10,45</t>
+          <t>-42,84; -10,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,49; 9,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-42,24; -10,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-65,49; 9,88</t>
+          <t>-66,76; 12,06</t>
         </is>
       </c>
     </row>
@@ -905,12 +805,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,55</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -919,16 +819,6 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-8,01</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-2,55</t>
         </is>
@@ -943,32 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,95; -2,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,96; 3,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -3,26</t>
+          <t>-12,95; -2,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 2,81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-13,54; -3,26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,84; 2,81</t>
+          <t>-7,96; 3,11</t>
         </is>
       </c>
     </row>
@@ -981,12 +861,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-28,16%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-8,95%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -995,16 +875,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-28,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-8,95%</t>
         </is>
@@ -1019,32 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,24; -11,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,04; 11,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,24; -11,64</t>
+          <t>-41,24; -11,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 10,95</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-43,24; -11,64</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-25,38; 10,95</t>
+          <t>-26,04; 11,99</t>
         </is>
       </c>
     </row>
@@ -1061,12 +921,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-12,51</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1075,16 +935,6 @@
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-12,51</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,53</t>
         </is>
@@ -1099,32 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,37; -7,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,25; 9,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -7,12</t>
+          <t>-18,37; -7,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 9,38</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-17,25; -7,12</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 9,38</t>
+          <t>-4,25; 9,25</t>
         </is>
       </c>
     </row>
@@ -1137,12 +977,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-46,89%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1151,16 +991,6 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-46,89%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>13,25%</t>
         </is>
@@ -1175,32 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,4; -32,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,93; 38,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,52; -28,93</t>
+          <t>-60,4; -32,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 38,57</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-58,52; -28,93</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-15,89; 38,57</t>
+          <t>-13,93; 38,7</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1037,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,04</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1231,16 +1051,6 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,04</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,68</t>
         </is>
@@ -1255,32 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,87; 1,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,65; 9,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 1,69</t>
+          <t>-8,87; 1,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,6</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-9,3; 1,69</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 9,6</t>
+          <t>-0,65; 9,75</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1093,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-24,44%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1307,16 +1107,6 @@
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-24,44%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>28,34%</t>
         </is>
@@ -1331,32 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-46,33; 8,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,82; 75,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 13,47</t>
+          <t>-46,33; 8,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 68,26</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-48,93; 13,47</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 68,26</t>
+          <t>-2,82; 75,36</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1153,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1387,16 +1167,6 @@
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
@@ -1411,32 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,29; -0,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,08; 7,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 0,01</t>
+          <t>-11,29; -0,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,82</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>-11,93; 0,01</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 6,82</t>
+          <t>-4,08; 7,14</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1209,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-38,05%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1463,16 +1223,6 @@
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-38,05%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>11,91%</t>
         </is>
@@ -1487,32 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-62,41; 0,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,38; 62,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 4,33</t>
+          <t>-62,41; 0,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 60,48</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-62,38; 4,33</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-23,96; 60,48</t>
+          <t>-21,38; 62,34</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1269,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,51</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1543,16 +1283,6 @@
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-9,51</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>0,14</t>
         </is>
@@ -1567,32 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,28; -4,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,28; 5,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -4,32</t>
+          <t>-15,28; -4,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,4</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-15,16; -4,32</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-5,96; 5,4</t>
+          <t>-6,28; 5,5</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1325,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-82,19%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1619,16 +1339,6 @@
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-82,19%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
@@ -1643,32 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-95,42; -40,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-36,67; 69,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,96; -42,02</t>
+          <t>-95,42; -40,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 64,88</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-95,96; -42,02</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-36,98; 64,88</t>
+          <t>-36,67; 69,14</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1385,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,46</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1699,16 +1399,6 @@
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-8,46</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-0,73</t>
         </is>
@@ -1723,32 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,67; -6,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,14; 1,83</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -6,45</t>
+          <t>-10,67; -6,35</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,74</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>-10,63; -6,45</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 1,74</t>
+          <t>-4,14; 1,83</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1441,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-35,36%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1775,16 +1455,6 @@
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-3,07%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-35,36%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-3,07%</t>
         </is>
@@ -1799,32 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,0; -27,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,57; 8,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,15; -28,23</t>
+          <t>-43,0; -27,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 7,53</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>-42,15; -28,23</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-16,22; 7,53</t>
+          <t>-16,57; 8,07</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1496,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A28:A31"/>

--- a/data/trans_camb/P42C_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Edad-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>8,13</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 1,99</t>
+          <t>-13,5; 2,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 27,62</t>
+          <t>-4,72; 22,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 1,99</t>
+          <t>-13,5; 2,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 27,62</t>
+          <t>-4,72; 22,42</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 9,93</t>
+          <t>-45,33; 10,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 115,19</t>
+          <t>-16,25; 89,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 9,93</t>
+          <t>-45,33; 10,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 115,19</t>
+          <t>-16,25; 89,78</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-7,33</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,33</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -2,65</t>
+          <t>-14,23; -2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 3,24</t>
+          <t>-8,06; 7,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -2,65</t>
+          <t>-14,23; -2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 3,24</t>
+          <t>-8,06; 7,03</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-24,65%</t>
+          <t>-1,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,65%</t>
+          <t>-1,3%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -10,14</t>
+          <t>-42,92; -8,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 12,06</t>
+          <t>-24,26; 26,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -10,14</t>
+          <t>-42,92; -8,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,76; 12,06</t>
+          <t>-24,26; 26,24</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-3,21</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,91</t>
+          <t>-13,42; -3,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,11</t>
+          <t>-8,29; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,91</t>
+          <t>-13,42; -3,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,11</t>
+          <t>-8,29; 2,03</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-8,95%</t>
+          <t>-11,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-8,95%</t>
+          <t>-11,29%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -11,38</t>
+          <t>-43,16; -12,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 11,99</t>
+          <t>-26,94; 7,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -11,38</t>
+          <t>-43,16; -12,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 11,99</t>
+          <t>-26,94; 7,9</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>6,31</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -7,88</t>
+          <t>-17,77; -7,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 9,25</t>
+          <t>0,92; 11,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -7,88</t>
+          <t>-17,77; -7,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 9,25</t>
+          <t>0,92; 11,65</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,4; -32,72</t>
+          <t>-58,87; -31,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 38,7</t>
+          <t>3,2; 49,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,4; -32,72</t>
+          <t>-58,87; -31,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 38,7</t>
+          <t>3,2; 49,36</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,88</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,88</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,18</t>
+          <t>-9,47; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,75</t>
+          <t>-0,06; 9,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,18</t>
+          <t>-9,47; 0,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 9,75</t>
+          <t>-0,06; 9,75</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 8,36</t>
+          <t>-48,14; 7,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 75,36</t>
+          <t>-0,33; 74,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 8,36</t>
+          <t>-48,14; 7,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 75,36</t>
+          <t>-0,33; 74,56</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,1</t>
+          <t>-12,1; -0,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 7,14</t>
+          <t>-3,5; 7,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,1</t>
+          <t>-12,1; -0,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 7,14</t>
+          <t>-3,5; 7,94</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 0,45</t>
+          <t>-64,32; 1,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 62,34</t>
+          <t>-19,9; 67,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 0,45</t>
+          <t>-64,32; 1,69</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 62,34</t>
+          <t>-19,9; 67,83</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -4,33</t>
+          <t>-14,9; -4,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,5</t>
+          <t>-5,54; 5,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -4,33</t>
+          <t>-14,9; -4,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,5</t>
+          <t>-5,54; 5,44</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-95,42; -40,94</t>
+          <t>-95,34; -40,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 69,14</t>
+          <t>-36,01; 65,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-95,42; -40,94</t>
+          <t>-95,34; -40,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 69,14</t>
+          <t>-36,01; 65,7</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,35</t>
+          <t>-10,67; -6,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,83</t>
+          <t>-2,14; 2,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -6,35</t>
+          <t>-10,67; -6,37</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,83</t>
+          <t>-2,14; 2,75</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-3,07%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -27,99</t>
+          <t>-42,36; -27,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 8,07</t>
+          <t>-8,57; 12,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-43,0; -27,99</t>
+          <t>-42,36; -27,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 8,07</t>
+          <t>-8,57; 12,2</t>
         </is>
       </c>
     </row>
